--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48C475DD-DC63-46E9-B113-8486763972A0}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2EF6DD-1A45-409F-8C41-27284956C2A4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1305,26 +1305,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B13" s="14">
+        <v>320</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>350</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2EF6DD-1A45-409F-8C41-27284956C2A4}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAF0DEDF-C818-4C2B-B7CD-845FD71F8AFA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1351,26 +1351,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B14" s="14">
+        <v>360</v>
+      </c>
+      <c r="C14" s="14">
+        <v>15</v>
+      </c>
+      <c r="D14" s="14">
+        <v>410</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
+        <v>180</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1205</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>235</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAF0DEDF-C818-4C2B-B7CD-845FD71F8AFA}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD88218-D4B1-4040-8551-F34263E246E6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1397,26 +1397,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B15" s="14">
+        <v>280</v>
+      </c>
+      <c r="C15" s="14">
+        <v>15</v>
+      </c>
+      <c r="D15" s="14">
+        <v>420</v>
+      </c>
+      <c r="E15" s="14">
+        <v>140</v>
+      </c>
+      <c r="F15" s="14">
+        <v>180</v>
+      </c>
+      <c r="G15" s="14">
+        <v>3</v>
+      </c>
+      <c r="H15" s="14">
+        <v>180</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1215</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>225</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD88218-D4B1-4040-8551-F34263E246E6}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{337106A9-1612-4AE5-8D58-3FBC79483F1D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Avg</t>
+  </si>
+  <si>
+    <t>satified</t>
   </si>
 </sst>
 </file>
@@ -1443,26 +1446,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B16" s="14">
+        <v>320</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>360</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>180</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{337106A9-1612-4AE5-8D58-3FBC79483F1D}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A047670-4F98-4949-BC5E-574B95421188}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1492,26 +1492,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B17" s="14">
+        <v>320</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>420</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A047670-4F98-4949-BC5E-574B95421188}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{478C4BA1-B57F-4DB2-977A-966C6A0FC92E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1538,26 +1538,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B18" s="14">
+        <v>300</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>40</v>
+      </c>
+      <c r="F18" s="14">
+        <v>420</v>
+      </c>
+      <c r="G18" s="14">
+        <v>7</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{478C4BA1-B57F-4DB2-977A-966C6A0FC92E}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924A2B9A-88CC-4BD4-B648-43C063A30859}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,18 @@
   </si>
   <si>
     <t>satified</t>
+  </si>
+  <si>
+    <t>Exhausted</t>
+  </si>
+  <si>
+    <t>Partially Satisfied</t>
+  </si>
+  <si>
+    <t>Consistent</t>
+  </si>
+  <si>
+    <t>Struggle</t>
   </si>
 </sst>
 </file>
@@ -1584,26 +1596,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B19" s="14">
+        <v>320</v>
+      </c>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
+      <c r="D19" s="14">
+        <v>300</v>
+      </c>
+      <c r="E19" s="14">
+        <v>46</v>
+      </c>
+      <c r="F19" s="14">
+        <v>400</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1126</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>314</v>
+      </c>
+      <c r="K19" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" t="s">
+        <v>67</v>
+      </c>
+      <c r="N19" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
@@ -10024,15 +10060,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K18 K20:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L18 L20:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M18 M20:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{924A2B9A-88CC-4BD4-B648-43C063A30859}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B9643D-A22F-47C4-9BCA-E863A1861720}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,18 @@
   </si>
   <si>
     <t>Struggle</t>
+  </si>
+  <si>
+    <t>Productive</t>
+  </si>
+  <si>
+    <t>Highly Satisfied</t>
+  </si>
+  <si>
+    <t>Fluctuating</t>
+  </si>
+  <si>
+    <t>Learning Focus</t>
   </si>
 </sst>
 </file>
@@ -1642,26 +1654,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B20" s="14">
+        <v>240</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>420</v>
+      </c>
+      <c r="E20" s="14">
+        <v>120</v>
+      </c>
+      <c r="F20" s="14">
+        <v>180</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3</v>
+      </c>
+      <c r="H20" s="14">
+        <v>55</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1045</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>395</v>
+      </c>
+      <c r="K20" t="s">
+        <v>69</v>
+      </c>
+      <c r="L20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M20" t="s">
+        <v>71</v>
+      </c>
+      <c r="N20" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
@@ -10060,15 +10096,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K18 K20:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K18 K21:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L18 L20:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L18 L21:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M18 M20:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M18 M21:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33B9643D-A22F-47C4-9BCA-E863A1861720}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E6E889-6BFF-47B5-95A6-41BB85BF63EE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Learning Focus</t>
+  </si>
+  <si>
+    <t>struggle</t>
   </si>
 </sst>
 </file>
@@ -1700,26 +1703,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B21" s="14">
+        <v>180</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>480</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>70</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77E6E889-6BFF-47B5-95A6-41BB85BF63EE}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2C2591-BEA1-40FF-91EC-52D0DD72F334}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1749,26 +1749,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B22" s="14">
+        <v>320</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>360</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2C2591-BEA1-40FF-91EC-52D0DD72F334}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95251A4-E22E-49F3-810B-088623A7A435}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1795,26 +1795,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B23" s="14">
+        <v>300</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>480</v>
+      </c>
+      <c r="E23" s="14">
+        <v>140</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>70</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D95251A4-E22E-49F3-810B-088623A7A435}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECAEB0F8-9433-4D5B-A10A-7785262EF69A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1840,27 +1840,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B24" s="14">
+        <v>310</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>390</v>
+      </c>
+      <c r="E24" s="14">
+        <v>43</v>
+      </c>
+      <c r="F24" s="14">
+        <v>420</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>80</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1243</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>197</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECAEB0F8-9433-4D5B-A10A-7785262EF69A}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DE32FA5-7538-4C6B-BD55-485DFECAB987}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>struggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good </t>
   </si>
 </sst>
 </file>
@@ -1887,26 +1890,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>340</v>
+      </c>
+      <c r="E25" s="14">
+        <v>38</v>
+      </c>
+      <c r="F25" s="14">
+        <v>420</v>
+      </c>
+      <c r="G25" s="14">
+        <v>7</v>
+      </c>
+      <c r="H25" s="14">
+        <v>45</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1293</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>147</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="238" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DE32FA5-7538-4C6B-BD55-485DFECAB987}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C52EA87-F31E-4BE7-A75E-9AEE10E35FCF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1936,26 +1936,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B26" s="14">
+        <v>380</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>420</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>180</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>

--- a/daily-log.xlsx
+++ b/daily-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/B0AA7295676BA96C/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C52EA87-F31E-4BE7-A75E-9AEE10E35FCF}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="8_{370DD9F5-B5DD-4EFC-93C9-87386ADFAB99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64A0F2C4-DBD1-48C6-8A9C-B2C40DAD24B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t xml:space="preserve">Good </t>
+  </si>
+  <si>
+    <t>medium</t>
   </si>
 </sst>
 </file>
@@ -1982,26 +1985,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B27" s="14">
+        <v>480</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>440</v>
+      </c>
+      <c r="E27" s="14">
+        <v>80</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>150</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
